--- a/Tables/Anthrone_mean.xlsx
+++ b/Tables/Anthrone_mean.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C116"/>
+  <dimension ref="A1:C117"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2069,7 +2069,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>121</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2078,21 +2078,36 @@
         </is>
       </c>
       <c r="C115">
-        <v>7.773947065976697</v>
+        <v>-402.5168053844945</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Dry</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>7.773947065976697</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Dry</t>
-        </is>
-      </c>
-      <c r="C116">
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Dry</t>
+        </is>
+      </c>
+      <c r="C117">
         <v>8.737615879184494</v>
       </c>
     </row>

--- a/Tables/Anthrone_mean.xlsx
+++ b/Tables/Anthrone_mean.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C117"/>
+  <dimension ref="A1:C116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -383,7 +383,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>22.56045605898341</v>
+        <v>22.56045605028024</v>
       </c>
     </row>
     <row r="3">
@@ -398,7 +398,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>23.57773606435104</v>
+        <v>23.57773605509791</v>
       </c>
     </row>
     <row r="4">
@@ -413,7 +413,7 @@
         </is>
       </c>
       <c r="C4">
-        <v>20.01243336577564</v>
+        <v>20.01243335646247</v>
       </c>
     </row>
     <row r="5">
@@ -428,7 +428,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>16.46255250652843</v>
+        <v>16.46255250047429</v>
       </c>
     </row>
     <row r="6">
@@ -443,7 +443,7 @@
         </is>
       </c>
       <c r="C6">
-        <v>17.36448275993919</v>
+        <v>17.3644827531011</v>
       </c>
     </row>
     <row r="7">
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="C7">
-        <v>23.9252430368245</v>
+        <v>23.92524302719237</v>
       </c>
     </row>
     <row r="8">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="C8">
-        <v>25.99299704425265</v>
+        <v>25.99299703303354</v>
       </c>
     </row>
     <row r="9">
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="C9">
-        <v>23.62036789755225</v>
+        <v>23.62036788611745</v>
       </c>
     </row>
     <row r="10">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="C10">
-        <v>18.54558816775328</v>
+        <v>18.54558816084357</v>
       </c>
     </row>
     <row r="11">
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="C11">
-        <v>24.04645149862444</v>
+        <v>24.04645148835931</v>
       </c>
     </row>
     <row r="12">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="C12">
-        <v>17.46510108058957</v>
+        <v>17.46510107426418</v>
       </c>
     </row>
     <row r="13">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="C13">
-        <v>29.33210623567831</v>
+        <v>29.33210622316335</v>
       </c>
     </row>
     <row r="14">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="C14">
-        <v>28.23920400201118</v>
+        <v>28.2392039887989</v>
       </c>
     </row>
     <row r="15">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C15">
-        <v>22.74212485124993</v>
+        <v>22.74212484348345</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="C16">
-        <v>23.32097985792451</v>
+        <v>23.32097984980452</v>
       </c>
     </row>
     <row r="17">
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="C17">
-        <v>18.89759737609407</v>
+        <v>18.89759736552361</v>
       </c>
     </row>
     <row r="18">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="C18">
-        <v>22.32510941365003</v>
+        <v>22.32510940366837</v>
       </c>
     </row>
     <row r="19">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C19">
-        <v>95.48600620574277</v>
+        <v>95.48600607369696</v>
       </c>
     </row>
     <row r="20">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="C20">
-        <v>18.80811865512351</v>
+        <v>18.80811864861735</v>
       </c>
     </row>
     <row r="21">
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="C21">
-        <v>24.4976317007525</v>
+        <v>24.49763168981905</v>
       </c>
     </row>
     <row r="22">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="C22">
-        <v>14.88730598580781</v>
+        <v>14.8873059809679</v>
       </c>
     </row>
     <row r="23">
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="C23">
-        <v>27.09436732741689</v>
+        <v>27.09436731596534</v>
       </c>
     </row>
     <row r="24">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C24">
-        <v>19.9762689970784</v>
+        <v>19.97626898929235</v>
       </c>
     </row>
     <row r="25">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="C25">
-        <v>13.19755851843058</v>
+        <v>13.19755851410578</v>
       </c>
     </row>
     <row r="26">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="C26">
-        <v>23.34720268592364</v>
+        <v>23.34720267670953</v>
       </c>
     </row>
     <row r="27">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="C27">
-        <v>11.97416145896406</v>
+        <v>11.97416145572017</v>
       </c>
     </row>
     <row r="28">
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="C28">
-        <v>32.70341464228048</v>
+        <v>32.70341463050234</v>
       </c>
     </row>
     <row r="29">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="C29">
-        <v>24.71364426984108</v>
+        <v>24.71364426048284</v>
       </c>
     </row>
     <row r="30">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="C30">
-        <v>17.4342706693333</v>
+        <v>17.43427066343899</v>
       </c>
     </row>
     <row r="31">
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="C31">
-        <v>17.84389489842059</v>
+        <v>17.84389489241031</v>
       </c>
     </row>
     <row r="32">
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="C32">
-        <v>14.90360441909995</v>
+        <v>14.90360441554135</v>
       </c>
     </row>
     <row r="33">
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C33">
-        <v>16.58665227513298</v>
+        <v>16.58665227063239</v>
       </c>
     </row>
     <row r="34">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="C34">
-        <v>13.90104507992682</v>
+        <v>13.9010450753318</v>
       </c>
     </row>
     <row r="35">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="C35">
-        <v>14.04450409947794</v>
+        <v>14.0445040932733</v>
       </c>
     </row>
     <row r="36">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="C36">
-        <v>9.329053064020266</v>
+        <v>9.329053061172669</v>
       </c>
     </row>
     <row r="37">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="C37">
-        <v>9.698454862836119</v>
+        <v>9.698454860384352</v>
       </c>
     </row>
     <row r="38">
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="C38">
-        <v>25.04552700019631</v>
+        <v>25.04552699147191</v>
       </c>
     </row>
     <row r="39">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="C39">
-        <v>5.350724304771354</v>
+        <v>5.350724302516621</v>
       </c>
     </row>
     <row r="40">
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="C40">
-        <v>17.09973970380888</v>
+        <v>17.09973969885293</v>
       </c>
     </row>
     <row r="41">
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="C41">
-        <v>19.23681054539415</v>
+        <v>19.23681053944058</v>
       </c>
     </row>
     <row r="42">
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C42">
-        <v>12.28743384018503</v>
+        <v>12.28743383737509</v>
       </c>
     </row>
     <row r="43">
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="C43">
-        <v>13.22284570218478</v>
+        <v>13.22284569868112</v>
       </c>
     </row>
     <row r="44">
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="C44">
-        <v>11.87406444327684</v>
+        <v>11.87406444006533</v>
       </c>
     </row>
     <row r="45">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="C45">
-        <v>25.73173340006241</v>
+        <v>25.73173338980673</v>
       </c>
     </row>
     <row r="46">
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="C46">
-        <v>14.17354647328509</v>
+        <v>14.17354646918703</v>
       </c>
     </row>
     <row r="47">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="C47">
-        <v>11.47579824375508</v>
+        <v>11.47579824099728</v>
       </c>
     </row>
     <row r="48">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="C48">
-        <v>11.13068975125315</v>
+        <v>11.13068974867508</v>
       </c>
     </row>
     <row r="49">
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="C49">
-        <v>11.62050386786022</v>
+        <v>11.62050386508256</v>
       </c>
     </row>
     <row r="50">
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="C50">
-        <v>11.84257145511052</v>
+        <v>11.8425714522331</v>
       </c>
     </row>
     <row r="51">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C51">
-        <v>23.4421533501836</v>
+        <v>23.44215334342972</v>
       </c>
     </row>
     <row r="52">
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="C52">
-        <v>15.03303747020667</v>
+        <v>15.0330374666885</v>
       </c>
     </row>
     <row r="53">
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="C53">
-        <v>11.62530046758755</v>
+        <v>11.62530046499677</v>
       </c>
     </row>
     <row r="54">
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="C54">
-        <v>13.32789214823012</v>
+        <v>13.3278921454108</v>
       </c>
     </row>
     <row r="55">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="C55">
-        <v>13.0238764343423</v>
+        <v>13.02387643119987</v>
       </c>
     </row>
     <row r="56">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C56">
-        <v>8.703067487161796</v>
+        <v>8.703067485152914</v>
       </c>
     </row>
     <row r="57">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="C57">
-        <v>10.60439742658196</v>
+        <v>10.60439742402762</v>
       </c>
     </row>
     <row r="58">
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="C58">
-        <v>14.21509624570077</v>
+        <v>14.21509624046008</v>
       </c>
     </row>
     <row r="59">
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="C59">
-        <v>13.46784215884074</v>
+        <v>13.4678421556573</v>
       </c>
     </row>
     <row r="60">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C60">
-        <v>21.56095976376418</v>
+        <v>21.56095975641283</v>
       </c>
     </row>
     <row r="61">
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="C61">
-        <v>15.32274401369812</v>
+        <v>15.32274400903107</v>
       </c>
     </row>
     <row r="62">
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="C62">
-        <v>9.064041672321506</v>
+        <v>9.06404167025234</v>
       </c>
     </row>
     <row r="63">
@@ -1298,7 +1298,7 @@
         </is>
       </c>
       <c r="C63">
-        <v>14.89970578222985</v>
+        <v>14.89970577780801</v>
       </c>
     </row>
     <row r="64">
@@ -1313,7 +1313,7 @@
         </is>
       </c>
       <c r="C64">
-        <v>16.04648406497902</v>
+        <v>16.04648405992454</v>
       </c>
     </row>
     <row r="65">
@@ -1328,7 +1328,7 @@
         </is>
       </c>
       <c r="C65">
-        <v>17.44713384337217</v>
+        <v>17.44713383766263</v>
       </c>
     </row>
     <row r="66">
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="C66">
-        <v>18.95684576238862</v>
+        <v>18.9568457542875</v>
       </c>
     </row>
     <row r="67">
@@ -1358,7 +1358,7 @@
         </is>
       </c>
       <c r="C67">
-        <v>9.790811849268477</v>
+        <v>9.790811847056522</v>
       </c>
     </row>
     <row r="68">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="C68">
-        <v>14.86996121308626</v>
+        <v>14.86996120739887</v>
       </c>
     </row>
     <row r="69">
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C69">
-        <v>15.95652154113297</v>
+        <v>15.95652153651683</v>
       </c>
     </row>
     <row r="70">
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="C70">
-        <v>12.24692873896039</v>
+        <v>12.24692873544948</v>
       </c>
     </row>
     <row r="71">
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="C71">
-        <v>22.95310960499393</v>
+        <v>22.95310959409341</v>
       </c>
     </row>
     <row r="72">
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="C72">
-        <v>10.05603280101736</v>
+        <v>10.05603279841014</v>
       </c>
     </row>
     <row r="73">
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="C73">
-        <v>14.13624746452084</v>
+        <v>14.13624745947199</v>
       </c>
     </row>
     <row r="74">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="C74">
-        <v>21.84542348833867</v>
+        <v>21.84542348176821</v>
       </c>
     </row>
     <row r="75">
@@ -1478,7 +1478,7 @@
         </is>
       </c>
       <c r="C75">
-        <v>9.103789040618189</v>
+        <v>9.103789036481977</v>
       </c>
     </row>
     <row r="76">
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="C76">
-        <v>17.96503994581183</v>
+        <v>17.96503993932219</v>
       </c>
     </row>
     <row r="77">
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="C77">
-        <v>11.08086443696076</v>
+        <v>11.08086443359894</v>
       </c>
     </row>
     <row r="78">
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C78">
-        <v>22.67627628615423</v>
+        <v>22.67627627726522</v>
       </c>
     </row>
     <row r="79">
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="C79">
-        <v>18.02974865509556</v>
+        <v>18.02974864976848</v>
       </c>
     </row>
     <row r="80">
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="C80">
-        <v>11.92190460610252</v>
+        <v>11.92190460326347</v>
       </c>
     </row>
     <row r="81">
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="C81">
-        <v>18.85804387361404</v>
+        <v>18.85804386769008</v>
       </c>
     </row>
     <row r="82">
@@ -1583,7 +1583,7 @@
         </is>
       </c>
       <c r="C82">
-        <v>20.05160153431135</v>
+        <v>20.05160152808657</v>
       </c>
     </row>
     <row r="83">
@@ -1598,7 +1598,7 @@
         </is>
       </c>
       <c r="C83">
-        <v>12.5956588667241</v>
+        <v>12.59565886241409</v>
       </c>
     </row>
     <row r="84">
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="C84">
-        <v>2.82558864807721</v>
+        <v>2.825588649272425</v>
       </c>
     </row>
     <row r="85">
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="C85">
-        <v>18.81169284864446</v>
+        <v>18.81169284246839</v>
       </c>
     </row>
     <row r="86">
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="C86">
-        <v>12.22063962442763</v>
+        <v>12.22063961967554</v>
       </c>
     </row>
     <row r="87">
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C87">
-        <v>9.135928326913849</v>
+        <v>9.135928324961483</v>
       </c>
     </row>
     <row r="88">
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="C88">
-        <v>13.11422808179434</v>
+        <v>13.11422807794479</v>
       </c>
     </row>
     <row r="89">
@@ -1688,7 +1688,7 @@
         </is>
       </c>
       <c r="C89">
-        <v>15.76624918342447</v>
+        <v>19.15272199784464</v>
       </c>
     </row>
     <row r="90">
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="C90">
-        <v>19.67718639461525</v>
+        <v>19.67718638770237</v>
       </c>
     </row>
     <row r="91">
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="C91">
-        <v>2.00821786915467</v>
+        <v>2.008217868517003</v>
       </c>
     </row>
     <row r="92">
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="C92">
-        <v>7.185489043355166</v>
+        <v>7.185489041332479</v>
       </c>
     </row>
     <row r="93">
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="C93">
-        <v>9.383727408376982</v>
+        <v>9.383727405379872</v>
       </c>
     </row>
     <row r="94">
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="C94">
-        <v>6.429178152156727</v>
+        <v>6.429178150409693</v>
       </c>
     </row>
     <row r="95">
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="C95">
-        <v>8.512740756017779</v>
+        <v>8.512740753194809</v>
       </c>
     </row>
     <row r="96">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C96">
-        <v>8.63010690736645</v>
+        <v>8.630106904380673</v>
       </c>
     </row>
     <row r="97">
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="C97">
-        <v>8.213870539679466</v>
+        <v>8.213870536888445</v>
       </c>
     </row>
     <row r="98">
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="C98">
-        <v>8.541341241563101</v>
+        <v>8.541341239086744</v>
       </c>
     </row>
     <row r="99">
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="C99">
-        <v>15.12737846985582</v>
+        <v>15.12737846090783</v>
       </c>
     </row>
     <row r="100">
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="C100">
-        <v>-0.1126773281403577</v>
+        <v>-0.1126773280395368</v>
       </c>
     </row>
     <row r="101">
@@ -1868,7 +1868,7 @@
         </is>
       </c>
       <c r="C101">
-        <v>1.206862380181664</v>
+        <v>1.206862379776768</v>
       </c>
     </row>
     <row r="102">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="C102">
-        <v>0.9904636353593192</v>
+        <v>0.9904636350507001</v>
       </c>
     </row>
     <row r="103">
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="C103">
-        <v>6.00719180916395</v>
+        <v>6.007191807496102</v>
       </c>
     </row>
     <row r="104">
@@ -1913,7 +1913,7 @@
         </is>
       </c>
       <c r="C104">
-        <v>9.725976143326397</v>
+        <v>9.725976139830486</v>
       </c>
     </row>
     <row r="105">
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C105">
-        <v>0.9549287217856175</v>
+        <v>0.9549287214791612</v>
       </c>
     </row>
     <row r="106">
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="C106">
-        <v>5.563356950817299</v>
+        <v>5.563356949352998</v>
       </c>
     </row>
     <row r="107">
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="C107">
-        <v>8.094204188490757</v>
+        <v>8.094204185963777</v>
       </c>
     </row>
     <row r="108">
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="C108">
-        <v>6.132256175196214</v>
+        <v>6.132256173329408</v>
       </c>
     </row>
     <row r="109">
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="C109">
-        <v>9.328810037114</v>
+        <v>9.328810033470987</v>
       </c>
     </row>
     <row r="110">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="C110">
-        <v>9.193058574094577</v>
+        <v>9.19305857062448</v>
       </c>
     </row>
     <row r="111">
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="C111">
-        <v>5.528729327459576</v>
+        <v>5.528729325585163</v>
       </c>
     </row>
     <row r="112">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="C112">
-        <v>1.495564174723957</v>
+        <v>1.495564174125406</v>
       </c>
     </row>
     <row r="113">
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="C113">
-        <v>1.628689021410428</v>
+        <v>1.628689020857489</v>
       </c>
     </row>
     <row r="114">
@@ -2063,13 +2063,13 @@
         </is>
       </c>
       <c r="C114">
-        <v>10.08450576423887</v>
+        <v>10.08450576106775</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>122</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2078,13 +2078,13 @@
         </is>
       </c>
       <c r="C115">
-        <v>-402.5168053844945</v>
+        <v>7.773947062599231</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>123</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2093,22 +2093,7 @@
         </is>
       </c>
       <c r="C116">
-        <v>7.773947065976697</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Dry</t>
-        </is>
-      </c>
-      <c r="C117">
-        <v>8.737615879184494</v>
+        <v>8.737615876631423</v>
       </c>
     </row>
   </sheetData>
